--- a/Homework 2/Homework 2 data.xlsx
+++ b/Homework 2/Homework 2 data.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -43,10 +43,10 @@
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -70,6 +70,14 @@
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -133,15 +141,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -157,20 +165,195 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1f497d"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="eeece1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4f81bd"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="c0504d"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9bbb59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064a2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4bacc6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="f79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ff"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D193"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D205"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="15.2"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -184,7 +367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="n">
         <v>39448</v>
       </c>
@@ -198,7 +381,7 @@
         <v>0.0021</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="n">
         <v>39479</v>
       </c>
@@ -212,7 +395,7 @@
         <v>0.0013</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="n">
         <v>39508</v>
       </c>
@@ -226,7 +409,7 @@
         <v>0.0017</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
         <v>39539</v>
       </c>
@@ -240,7 +423,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="n">
         <v>39569</v>
       </c>
@@ -254,7 +437,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="n">
         <v>39600</v>
       </c>
@@ -268,7 +451,7 @@
         <v>0.0017</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="n">
         <v>39630</v>
       </c>
@@ -282,7 +465,7 @@
         <v>0.0015</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="n">
         <v>39661</v>
       </c>
@@ -296,7 +479,7 @@
         <v>0.0013</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="n">
         <v>39692</v>
       </c>
@@ -310,7 +493,7 @@
         <v>0.0015</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="n">
         <v>39722</v>
       </c>
@@ -324,7 +507,7 @@
         <v>0.0008</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="n">
         <v>39753</v>
       </c>
@@ -338,7 +521,7 @@
         <v>0.0003</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="n">
         <v>39783</v>
       </c>
@@ -352,7 +535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="n">
         <v>39814</v>
       </c>
@@ -366,7 +549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="n">
         <v>39845</v>
       </c>
@@ -380,7 +563,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="n">
         <v>39873</v>
       </c>
@@ -394,7 +577,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="n">
         <v>39904</v>
       </c>
@@ -408,7 +591,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="n">
         <v>39934</v>
       </c>
@@ -422,7 +605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="n">
         <v>39965</v>
       </c>
@@ -436,7 +619,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="n">
         <v>39995</v>
       </c>
@@ -450,7 +633,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="n">
         <v>40026</v>
       </c>
@@ -464,7 +647,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="n">
         <v>40057</v>
       </c>
@@ -478,7 +661,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="n">
         <v>40087</v>
       </c>
@@ -492,7 +675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="n">
         <v>40118</v>
       </c>
@@ -506,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="n">
         <v>40148</v>
       </c>
@@ -520,7 +703,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="n">
         <v>40179</v>
       </c>
@@ -534,7 +717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="n">
         <v>40210</v>
       </c>
@@ -548,7 +731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="n">
         <v>40238</v>
       </c>
@@ -562,7 +745,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="n">
         <v>40269</v>
       </c>
@@ -576,7 +759,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="4" t="n">
         <v>40299</v>
       </c>
@@ -590,7 +773,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="n">
         <v>40330</v>
       </c>
@@ -604,7 +787,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="n">
         <v>40360</v>
       </c>
@@ -618,7 +801,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="n">
         <v>40391</v>
       </c>
@@ -632,7 +815,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="n">
         <v>40422</v>
       </c>
@@ -646,7 +829,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="n">
         <v>40452</v>
       </c>
@@ -660,7 +843,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="n">
         <v>40483</v>
       </c>
@@ -674,7 +857,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="n">
         <v>40513</v>
       </c>
@@ -688,7 +871,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="4" t="n">
         <v>40544</v>
       </c>
@@ -702,7 +885,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="n">
         <v>40575</v>
       </c>
@@ -716,7 +899,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="4" t="n">
         <v>40603</v>
       </c>
@@ -730,7 +913,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="n">
         <v>40634</v>
       </c>
@@ -744,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="n">
         <v>40664</v>
       </c>
@@ -758,7 +941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="n">
         <v>40695</v>
       </c>
@@ -772,7 +955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="n">
         <v>40725</v>
       </c>
@@ -786,7 +969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="n">
         <v>40756</v>
       </c>
@@ -800,7 +983,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="n">
         <v>40787</v>
       </c>
@@ -814,7 +997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="n">
         <v>40817</v>
       </c>
@@ -828,7 +1011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="4" t="n">
         <v>40848</v>
       </c>
@@ -842,7 +1025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="n">
         <v>40878</v>
       </c>
@@ -856,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="4" t="n">
         <v>40909</v>
       </c>
@@ -870,7 +1053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="n">
         <v>40940</v>
       </c>
@@ -884,7 +1067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="n">
         <v>40969</v>
       </c>
@@ -898,7 +1081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="n">
         <v>41000</v>
       </c>
@@ -912,7 +1095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="n">
         <v>41030</v>
       </c>
@@ -926,7 +1109,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="n">
         <v>41061</v>
       </c>
@@ -940,7 +1123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="n">
         <v>41091</v>
       </c>
@@ -954,7 +1137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="n">
         <v>41122</v>
       </c>
@@ -968,7 +1151,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="n">
         <v>41153</v>
       </c>
@@ -982,7 +1165,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="n">
         <v>41183</v>
       </c>
@@ -996,7 +1179,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="n">
         <v>41214</v>
       </c>
@@ -1010,7 +1193,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="n">
         <v>41244</v>
       </c>
@@ -1024,7 +1207,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="n">
         <v>41275</v>
       </c>
@@ -1038,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="n">
         <v>41306</v>
       </c>
@@ -1052,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="n">
         <v>41334</v>
       </c>
@@ -1066,7 +1249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="n">
         <v>41365</v>
       </c>
@@ -1080,7 +1263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="n">
         <v>41395</v>
       </c>
@@ -1094,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="n">
         <v>41426</v>
       </c>
@@ -1108,7 +1291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="n">
         <v>41456</v>
       </c>
@@ -1122,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="n">
         <v>41487</v>
       </c>
@@ -1136,7 +1319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="n">
         <v>41518</v>
       </c>
@@ -1150,7 +1333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="n">
         <v>41548</v>
       </c>
@@ -1164,7 +1347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="n">
         <v>41579</v>
       </c>
@@ -1178,7 +1361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="n">
         <v>41609</v>
       </c>
@@ -1192,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="n">
         <v>41640</v>
       </c>
@@ -1206,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="n">
         <v>41671</v>
       </c>
@@ -1220,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="4" t="n">
         <v>41699</v>
       </c>
@@ -1234,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="n">
         <v>41730</v>
       </c>
@@ -1248,7 +1431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="4" t="n">
         <v>41760</v>
       </c>
@@ -1262,7 +1445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="n">
         <v>41791</v>
       </c>
@@ -1276,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="4" t="n">
         <v>41821</v>
       </c>
@@ -1290,7 +1473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="n">
         <v>41852</v>
       </c>
@@ -1304,7 +1487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="4" t="n">
         <v>41883</v>
       </c>
@@ -1318,7 +1501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="n">
         <v>41913</v>
       </c>
@@ -1332,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="4" t="n">
         <v>41944</v>
       </c>
@@ -1346,7 +1529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="n">
         <v>41974</v>
       </c>
@@ -1360,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="4" t="n">
         <v>42005</v>
       </c>
@@ -1374,7 +1557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="n">
         <v>42036</v>
       </c>
@@ -1388,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="4" t="n">
         <v>42064</v>
       </c>
@@ -1402,7 +1585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="n">
         <v>42095</v>
       </c>
@@ -1416,7 +1599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="4" t="n">
         <v>42125</v>
       </c>
@@ -1430,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="n">
         <v>42156</v>
       </c>
@@ -1444,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="n">
         <v>42186</v>
       </c>
@@ -1458,7 +1641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="n">
         <v>42217</v>
       </c>
@@ -1472,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="n">
         <v>42248</v>
       </c>
@@ -1486,7 +1669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="n">
         <v>42278</v>
       </c>
@@ -1500,7 +1683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="n">
         <v>42309</v>
       </c>
@@ -1514,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="n">
         <v>42339</v>
       </c>
@@ -1528,7 +1711,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="n">
         <v>42370</v>
       </c>
@@ -1542,7 +1725,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="n">
         <v>42401</v>
       </c>
@@ -1556,7 +1739,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="n">
         <v>42430</v>
       </c>
@@ -1570,7 +1753,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="n">
         <v>42461</v>
       </c>
@@ -1584,7 +1767,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="4" t="n">
         <v>42491</v>
       </c>
@@ -1598,7 +1781,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="n">
         <v>42522</v>
       </c>
@@ -1612,7 +1795,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="4" t="n">
         <v>42552</v>
       </c>
@@ -1626,7 +1809,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="n">
         <v>42583</v>
       </c>
@@ -1640,7 +1823,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="4" t="n">
         <v>42614</v>
       </c>
@@ -1654,7 +1837,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="n">
         <v>42644</v>
       </c>
@@ -1668,7 +1851,7 @@
         <v>0.0002</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="4" t="n">
         <v>42675</v>
       </c>
@@ -1682,7 +1865,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="n">
         <v>42705</v>
       </c>
@@ -1696,7 +1879,7 @@
         <v>0.0003</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="4" t="n">
         <v>42736</v>
       </c>
@@ -1710,7 +1893,7 @@
         <v>0.0004</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="n">
         <v>42767</v>
       </c>
@@ -1724,7 +1907,7 @@
         <v>0.0004</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="4" t="n">
         <v>42795</v>
       </c>
@@ -1738,7 +1921,7 @@
         <v>0.0003</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="n">
         <v>42826</v>
       </c>
@@ -1746,13 +1929,13 @@
         <v>0.010181</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>0.019208</v>
+        <v>0.019207</v>
       </c>
       <c r="D113" s="1" t="n">
         <v>0.0005</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="4" t="n">
         <v>42856</v>
       </c>
@@ -1766,7 +1949,7 @@
         <v>0.0006</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="n">
         <v>42887</v>
       </c>
@@ -1780,7 +1963,7 @@
         <v>0.0006</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="4" t="n">
         <v>42917</v>
       </c>
@@ -1794,7 +1977,7 @@
         <v>0.0007</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="n">
         <v>42948</v>
       </c>
@@ -1808,7 +1991,7 @@
         <v>0.0009</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="4" t="n">
         <v>42979</v>
       </c>
@@ -1822,7 +2005,7 @@
         <v>0.0009</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="n">
         <v>43009</v>
       </c>
@@ -1836,7 +2019,7 @@
         <v>0.0009</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="4" t="n">
         <v>43040</v>
       </c>
@@ -1850,7 +2033,7 @@
         <v>0.0008</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="n">
         <v>43070</v>
       </c>
@@ -1864,7 +2047,7 @@
         <v>0.0009</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="4" t="n">
         <v>43101</v>
       </c>
@@ -1875,10 +2058,10 @@
         <v>0.036136</v>
       </c>
       <c r="D122" s="1" t="n">
-        <v>0.0012</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0011</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="n">
         <v>43132</v>
       </c>
@@ -1892,7 +2075,7 @@
         <v>0.0011</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="4" t="n">
         <v>43160</v>
       </c>
@@ -1903,10 +2086,10 @@
         <v>0.002727</v>
       </c>
       <c r="D124" s="1" t="n">
-        <v>0.0011</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="n">
         <v>43191</v>
       </c>
@@ -1920,7 +2103,7 @@
         <v>0.0014</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="4" t="n">
         <v>43221</v>
       </c>
@@ -1934,7 +2117,7 @@
         <v>0.0014</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="n">
         <v>43252</v>
       </c>
@@ -1948,7 +2131,7 @@
         <v>0.0014</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="4" t="n">
         <v>43282</v>
       </c>
@@ -1962,7 +2145,7 @@
         <v>0.0016</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>43313</v>
       </c>
@@ -1976,7 +2159,7 @@
         <v>0.0016</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>43344</v>
       </c>
@@ -1990,7 +2173,7 @@
         <v>0.0015</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>43374</v>
       </c>
@@ -2004,7 +2187,7 @@
         <v>0.0019</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>43405</v>
       </c>
@@ -2018,7 +2201,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="n">
         <v>43435</v>
       </c>
@@ -2029,10 +2212,10 @@
         <v>0.050145</v>
       </c>
       <c r="D133" s="1" t="n">
-        <v>0.002</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0019</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="4" t="n">
         <v>43466</v>
       </c>
@@ -2046,7 +2229,7 @@
         <v>0.0021</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="n">
         <v>43497</v>
       </c>
@@ -2060,7 +2243,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="4" t="n">
         <v>43525</v>
       </c>
@@ -2074,7 +2257,7 @@
         <v>0.0019</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="n">
         <v>43556</v>
       </c>
@@ -2088,7 +2271,7 @@
         <v>0.0021</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="4" t="n">
         <v>43586</v>
       </c>
@@ -2102,7 +2285,7 @@
         <v>0.0021</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="n">
         <v>43617</v>
       </c>
@@ -2116,7 +2299,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="4" t="n">
         <v>43647</v>
       </c>
@@ -2130,7 +2313,7 @@
         <v>0.0019</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="n">
         <v>43678</v>
       </c>
@@ -2144,7 +2327,7 @@
         <v>0.0016</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="4" t="n">
         <v>43709</v>
       </c>
@@ -2158,7 +2341,7 @@
         <v>0.0018</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="n">
         <v>43739</v>
       </c>
@@ -2169,10 +2352,10 @@
         <v>0.012638</v>
       </c>
       <c r="D143" s="1" t="n">
-        <v>0.0016</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0015</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="4" t="n">
         <v>43770</v>
       </c>
@@ -2186,7 +2369,7 @@
         <v>0.0012</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="n">
         <v>43800</v>
       </c>
@@ -2200,7 +2383,7 @@
         <v>0.0014</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="4" t="n">
         <v>43831</v>
       </c>
@@ -2214,7 +2397,7 @@
         <v>0.0013</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="n">
         <v>43862</v>
       </c>
@@ -2228,7 +2411,7 @@
         <v>0.0012</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="4" t="n">
         <v>43891</v>
       </c>
@@ -2239,10 +2422,10 @@
         <v>-0.013343</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>0.0013</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0012</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="n">
         <v>43922</v>
       </c>
@@ -2256,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="4" t="n">
         <v>43952</v>
       </c>
@@ -2270,7 +2453,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="n">
         <v>43983</v>
       </c>
@@ -2284,7 +2467,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="4" t="n">
         <v>44013</v>
       </c>
@@ -2298,7 +2481,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="n">
         <v>44044</v>
       </c>
@@ -2312,7 +2495,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="4" t="n">
         <v>44075</v>
       </c>
@@ -2326,7 +2509,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="n">
         <v>44105</v>
       </c>
@@ -2340,7 +2523,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="4" t="n">
         <v>44136</v>
       </c>
@@ -2354,7 +2537,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="n">
         <v>44166</v>
       </c>
@@ -2368,7 +2551,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="4" t="n">
         <v>44197</v>
       </c>
@@ -2379,10 +2562,10 @@
         <v>-0.020306</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="n">
         <v>44228</v>
       </c>
@@ -2396,7 +2579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="4" t="n">
         <v>44256</v>
       </c>
@@ -2410,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="n">
         <v>44287</v>
       </c>
@@ -2424,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="4" t="n">
         <v>44317</v>
       </c>
@@ -2438,7 +2621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="n">
         <v>44348</v>
       </c>
@@ -2452,7 +2635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="4" t="n">
         <v>44378</v>
       </c>
@@ -2460,13 +2643,13 @@
         <v>0.02362</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>0.040079</v>
+        <v>0.040078</v>
       </c>
       <c r="D164" s="1" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="n">
         <v>44409</v>
       </c>
@@ -2480,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="4" t="n">
         <v>44440</v>
       </c>
@@ -2494,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="n">
         <v>44470</v>
       </c>
@@ -2508,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="4" t="n">
         <v>44501</v>
       </c>
@@ -2522,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="n">
         <v>44531</v>
       </c>
@@ -2536,7 +2719,7 @@
         <v>0.0001</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="4" t="n">
         <v>44562</v>
       </c>
@@ -2550,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="n">
         <v>44593</v>
       </c>
@@ -2564,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="4" t="n">
         <v>44621</v>
       </c>
@@ -2575,10 +2758,10 @@
         <v>0.010928</v>
       </c>
       <c r="D172" s="1" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="n">
         <v>44652</v>
       </c>
@@ -2589,10 +2772,10 @@
         <v>-0.004496</v>
       </c>
       <c r="D173" s="1" t="n">
-        <v>0.0001</v>
-      </c>
-    </row>
-    <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="4" t="n">
         <v>44682</v>
       </c>
@@ -2606,7 +2789,7 @@
         <v>0.0003</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="n">
         <v>44713</v>
       </c>
@@ -2620,7 +2803,7 @@
         <v>0.0006</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="4" t="n">
         <v>44743</v>
       </c>
@@ -2634,7 +2817,7 @@
         <v>0.0008</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="n">
         <v>44774</v>
       </c>
@@ -2648,7 +2831,7 @@
         <v>0.0019</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="4" t="n">
         <v>44805</v>
       </c>
@@ -2662,7 +2845,7 @@
         <v>0.0019</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="n">
         <v>44835</v>
       </c>
@@ -2676,7 +2859,7 @@
         <v>0.0023</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="4" t="n">
         <v>44866</v>
       </c>
@@ -2690,7 +2873,7 @@
         <v>0.0029</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="n">
         <v>44896</v>
       </c>
@@ -2704,7 +2887,7 @@
         <v>0.0033</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="4" t="n">
         <v>44927</v>
       </c>
@@ -2718,7 +2901,7 @@
         <v>0.0035</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="n">
         <v>44958</v>
       </c>
@@ -2732,7 +2915,7 @@
         <v>0.0034</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="4" t="n">
         <v>44986</v>
       </c>
@@ -2746,7 +2929,7 @@
         <v>0.0036</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="n">
         <v>45017</v>
       </c>
@@ -2760,7 +2943,7 @@
         <v>0.0035</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="4" t="n">
         <v>45047</v>
       </c>
@@ -2774,7 +2957,7 @@
         <v>0.0036</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="n">
         <v>45078</v>
       </c>
@@ -2788,7 +2971,7 @@
         <v>0.004</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="4" t="n">
         <v>45108</v>
       </c>
@@ -2802,7 +2985,7 @@
         <v>0.0045</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="n">
         <v>45139</v>
       </c>
@@ -2816,7 +2999,7 @@
         <v>0.0045</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="4" t="n">
         <v>45170</v>
       </c>
@@ -2830,7 +3013,7 @@
         <v>0.0043</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="n">
         <v>45200</v>
       </c>
@@ -2844,7 +3027,7 @@
         <v>0.0047</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="4" t="n">
         <v>45231</v>
       </c>
@@ -2858,7 +3041,7 @@
         <v>0.0044</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="n">
         <v>45261</v>
       </c>
@@ -2866,10 +3049,178 @@
         <v>0.045303</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>0.019604</v>
+        <v>0.012047</v>
       </c>
       <c r="D193" s="1" t="n">
         <v>0.0043</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>0.01668</v>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>-0.011879</v>
+      </c>
+      <c r="D194" s="1" t="n">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B195" s="1" t="n">
+        <v>0.053287</v>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>-0.002503</v>
+      </c>
+      <c r="D195" s="1" t="n">
+        <v>0.0042</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>0.032053</v>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>0.085695</v>
+      </c>
+      <c r="D196" s="1" t="n">
+        <v>0.0043</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>-0.040956</v>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>0.048845</v>
+      </c>
+      <c r="D197" s="1" t="n">
+        <v>0.0047</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>0.049457</v>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>0.012139</v>
+      </c>
+      <c r="D198" s="1" t="n">
+        <v>0.0044</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>0.035757</v>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>-0.00653</v>
+      </c>
+      <c r="D199" s="1" t="n">
+        <v>0.0041</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>0.012047</v>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>0.039526</v>
+      </c>
+      <c r="D200" s="1" t="n">
+        <v>0.0045</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>0.024141</v>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>0.04321</v>
+      </c>
+      <c r="D201" s="1" t="n">
+        <v>0.0048</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>0.021226</v>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>0.049918</v>
+      </c>
+      <c r="D202" s="1" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>-0.009158</v>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>0.048771</v>
+      </c>
+      <c r="D203" s="1" t="n">
+        <v>0.0039</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>0.058566</v>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>-0.041412</v>
+      </c>
+      <c r="D204" s="1" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>-0.023956</v>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>-0.020062</v>
+      </c>
+      <c r="D205" s="1" t="n">
+        <v>0.0037</v>
       </c>
     </row>
   </sheetData>
